--- a/배차작업/근무조편성/본사_근무표_AI이용한자동추출-오류있음.xlsx
+++ b/배차작업/근무조편성/본사_근무표_AI이용한자동추출-오류있음.xlsx
@@ -1716,14 +1716,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BE53"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <dimension ref="A1:BE48"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="57" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="19.95" customHeight="1">
+    <row r="1" spans="1:57" ht="24.6" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="AF1" s="14"/>
       <c r="AG1" s="14"/>
     </row>
-    <row r="2" spans="1:57" ht="19.95" customHeight="1">
+    <row r="2" spans="1:57" ht="18" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1837,7 +1837,7 @@
       <c r="BD2" s="16"/>
       <c r="BE2" s="16"/>
     </row>
-    <row r="3" spans="1:57" ht="19.95" customHeight="1">
+    <row r="3" spans="1:57" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="19.95" customHeight="1">
+    <row r="4" spans="1:57" ht="18" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>67</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="19.95" customHeight="1">
+    <row r="5" spans="1:57" ht="18" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>75</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="19.95" customHeight="1">
+    <row r="6" spans="1:57" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>78</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="19.95" customHeight="1">
+    <row r="7" spans="1:57" ht="18" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>81</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="19.95" customHeight="1">
+    <row r="8" spans="1:57" ht="18" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>82</v>
       </c>
@@ -2875,8 +2875,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="19.95" customHeight="1"/>
-    <row r="10" spans="1:57" ht="19.95" customHeight="1">
+    <row r="10" spans="1:57" ht="18" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -2953,7 +2952,7 @@
       <c r="BD10" s="16"/>
       <c r="BE10" s="16"/>
     </row>
-    <row r="11" spans="1:57" ht="19.95" customHeight="1">
+    <row r="11" spans="1:57" ht="18" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -3126,7 +3125,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:57" ht="19.95" customHeight="1">
+    <row r="12" spans="1:57" ht="18" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>67</v>
       </c>
@@ -3299,7 +3298,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:57" ht="19.95" customHeight="1">
+    <row r="13" spans="1:57" ht="18" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>75</v>
       </c>
@@ -3472,7 +3471,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:57" ht="19.95" customHeight="1">
+    <row r="14" spans="1:57" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>78</v>
       </c>
@@ -3645,7 +3644,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:57" ht="19.95" customHeight="1">
+    <row r="15" spans="1:57" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>81</v>
       </c>
@@ -3818,7 +3817,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="16" spans="1:57" ht="19.95" customHeight="1">
+    <row r="16" spans="1:57" ht="18" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>82</v>
       </c>
@@ -3991,8 +3990,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:57" ht="19.95" customHeight="1"/>
-    <row r="18" spans="1:57" ht="19.95" customHeight="1">
+    <row r="18" spans="1:57" ht="18" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -4069,7 +4067,7 @@
       <c r="BD18" s="16"/>
       <c r="BE18" s="16"/>
     </row>
-    <row r="19" spans="1:57" ht="19.95" customHeight="1">
+    <row r="19" spans="1:57" ht="18" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -4242,7 +4240,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:57" ht="19.95" customHeight="1">
+    <row r="20" spans="1:57" ht="18" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>67</v>
       </c>
@@ -4415,7 +4413,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:57" ht="19.95" customHeight="1">
+    <row r="21" spans="1:57" ht="18" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>75</v>
       </c>
@@ -4588,7 +4586,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:57" ht="19.95" customHeight="1">
+    <row r="22" spans="1:57" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>78</v>
       </c>
@@ -4761,7 +4759,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:57" ht="19.95" customHeight="1">
+    <row r="23" spans="1:57" ht="18" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>81</v>
       </c>
@@ -4934,7 +4932,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:57" ht="19.95" customHeight="1">
+    <row r="24" spans="1:57" ht="18" customHeight="1">
       <c r="A24" s="11" t="s">
         <v>82</v>
       </c>
@@ -5107,8 +5105,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:57" ht="19.95" customHeight="1"/>
-    <row r="26" spans="1:57" ht="19.95" customHeight="1">
+    <row r="26" spans="1:57" ht="18" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -5185,7 +5182,7 @@
       <c r="BD26" s="16"/>
       <c r="BE26" s="16"/>
     </row>
-    <row r="27" spans="1:57" ht="19.95" customHeight="1">
+    <row r="27" spans="1:57" ht="18" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -5358,7 +5355,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="28" spans="1:57" ht="19.95" customHeight="1">
+    <row r="28" spans="1:57" ht="18" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>67</v>
       </c>
@@ -5531,7 +5528,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:57" ht="19.95" customHeight="1">
+    <row r="29" spans="1:57" ht="18" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>75</v>
       </c>
@@ -5704,7 +5701,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="30" spans="1:57" ht="19.95" customHeight="1">
+    <row r="30" spans="1:57" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>78</v>
       </c>
@@ -5877,7 +5874,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="31" spans="1:57" ht="19.95" customHeight="1">
+    <row r="31" spans="1:57" ht="18" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>81</v>
       </c>
@@ -6050,7 +6047,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:57" ht="19.95" customHeight="1">
+    <row r="32" spans="1:57" ht="18" customHeight="1">
       <c r="A32" s="11" t="s">
         <v>82</v>
       </c>
@@ -6223,8 +6220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:57" ht="19.95" customHeight="1"/>
-    <row r="34" spans="1:57" ht="19.95" customHeight="1">
+    <row r="34" spans="1:57" ht="18" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -6301,7 +6297,7 @@
       <c r="BD34" s="16"/>
       <c r="BE34" s="16"/>
     </row>
-    <row r="35" spans="1:57" ht="19.95" customHeight="1">
+    <row r="35" spans="1:57" ht="18" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -6474,7 +6470,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:57" ht="19.95" customHeight="1">
+    <row r="36" spans="1:57" ht="18" customHeight="1">
       <c r="A36" s="15" t="s">
         <v>67</v>
       </c>
@@ -6647,7 +6643,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="1:57" ht="19.95" customHeight="1">
+    <row r="37" spans="1:57" ht="18" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>75</v>
       </c>
@@ -6820,7 +6816,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="38" spans="1:57" ht="19.95" customHeight="1">
+    <row r="38" spans="1:57" ht="18" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>78</v>
       </c>
@@ -6993,7 +6989,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="39" spans="1:57" ht="19.95" customHeight="1">
+    <row r="39" spans="1:57" ht="18" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>81</v>
       </c>
@@ -7166,7 +7162,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:57" ht="19.95" customHeight="1">
+    <row r="40" spans="1:57" ht="18" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>82</v>
       </c>
@@ -7339,8 +7335,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:57" ht="19.95" customHeight="1"/>
-    <row r="42" spans="1:57" ht="19.95" customHeight="1">
+    <row r="42" spans="1:57" ht="18" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
@@ -7417,7 +7412,7 @@
       <c r="BD42" s="16"/>
       <c r="BE42" s="16"/>
     </row>
-    <row r="43" spans="1:57" ht="19.95" customHeight="1">
+    <row r="43" spans="1:57" ht="18" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>10</v>
       </c>
@@ -7590,7 +7585,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="44" spans="1:57" ht="19.95" customHeight="1">
+    <row r="44" spans="1:57" ht="18" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>67</v>
       </c>
@@ -7763,7 +7758,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:57" ht="19.95" customHeight="1">
+    <row r="45" spans="1:57" ht="18" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>75</v>
       </c>
@@ -7936,7 +7931,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="46" spans="1:57" ht="19.95" customHeight="1">
+    <row r="46" spans="1:57" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
         <v>78</v>
       </c>
@@ -8109,7 +8104,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="47" spans="1:57" ht="19.95" customHeight="1">
+    <row r="47" spans="1:57" ht="18" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>81</v>
       </c>
@@ -8282,7 +8277,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:57" ht="19.95" customHeight="1">
+    <row r="48" spans="1:57" ht="18" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>82</v>
       </c>
@@ -8455,11 +8450,6 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" ht="19.95" customHeight="1"/>
-    <row r="50" ht="19.95" customHeight="1"/>
-    <row r="51" ht="19.95" customHeight="1"/>
-    <row r="52" ht="19.95" customHeight="1"/>
-    <row r="53" ht="19.95" customHeight="1"/>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="A44"/>
